--- a/Thesis Forecasting/PAPER CONTEXT/tables/appendix_picture_catalog.xlsx
+++ b/Thesis Forecasting/PAPER CONTEXT/tables/appendix_picture_catalog.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$K$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$K$67</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -506,7 +506,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>appendix_materials/figures/appendix_I_testing_plots/benchmark_actual_testing_plots/agus1_actual_vs_benchmark_testing.png</t>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/benchmark_actual_testing_plots/agus1_actual_vs_benchmark_testing.png</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -561,7 +561,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>appendix_materials/figures/appendix_I_testing_plots/benchmark_actual_testing_plots/agus2_actual_vs_benchmark_testing.png</t>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/benchmark_actual_testing_plots/agus2_actual_vs_benchmark_testing.png</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -616,7 +616,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>appendix_materials/figures/appendix_I_testing_plots/benchmark_actual_testing_plots/agus4_actual_vs_benchmark_testing.png</t>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/benchmark_actual_testing_plots/agus4_actual_vs_benchmark_testing.png</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>appendix_materials/figures/appendix_I_testing_plots/benchmark_actual_testing_plots/agus5_actual_vs_benchmark_testing.png</t>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/benchmark_actual_testing_plots/agus5_actual_vs_benchmark_testing.png</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>appendix_materials/figures/appendix_I_testing_plots/benchmark_actual_testing_plots/agus6_actual_vs_benchmark_testing.png</t>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/benchmark_actual_testing_plots/agus6_actual_vs_benchmark_testing.png</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>appendix_materials/figures/appendix_I_testing_plots/benchmark_actual_testing_plots/agus7_actual_vs_benchmark_testing.png</t>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/benchmark_actual_testing_plots/agus7_actual_vs_benchmark_testing.png</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>appendix_materials/figures/appendix_I_testing_plots/benchmark_actual_testing_plots/all_plants_actual_vs_benchmark_testing.png</t>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/benchmark_actual_testing_plots/all_plants_actual_vs_benchmark_testing.png</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>appendix_materials/figures/appendix_I_testing_plots/benchmark_comparison/testing_mape_model_comparison.png</t>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/benchmark_comparison/testing_mape_model_comparison.png</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -915,7 +915,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>82.38</v>
+        <v>89.69</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>appendix_materials/figures/appendix_I_testing_plots/benchmark_comparison/testing_rmse_model_comparison.png</t>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/benchmark_comparison/testing_rmse_model_comparison.png</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -970,7 +970,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>78.8</v>
+        <v>89.7</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>appendix_materials/figures/appendix_I_testing_plots/cleaned_profiles/figure_4_01_agus1_cleaned_profile.png</t>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/cleaned_profiles/figure_4_01_agus1_cleaned_profile.png</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>appendix_materials/figures/appendix_I_testing_plots/cleaned_profiles/figure_4_02_agus2_cleaned_profile.png</t>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/cleaned_profiles/figure_4_02_agus2_cleaned_profile.png</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>appendix_materials/figures/appendix_I_testing_plots/cleaned_profiles/figure_4_03_agus4_cleaned_profile.png</t>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/cleaned_profiles/figure_4_03_agus4_cleaned_profile.png</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>230.98</v>
+        <v>230.97</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>appendix_materials/figures/appendix_I_testing_plots/cleaned_profiles/figure_4_04_agus5_cleaned_profile.png</t>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/cleaned_profiles/figure_4_04_agus5_cleaned_profile.png</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>appendix_materials/figures/appendix_I_testing_plots/cleaned_profiles/figure_4_05_agus6_cleaned_profile.png</t>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/cleaned_profiles/figure_4_05_agus6_cleaned_profile.png</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>appendix_materials/figures/appendix_I_testing_plots/cleaned_profiles/figure_4_06_agus7_cleaned_profile.png</t>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/cleaned_profiles/figure_4_06_agus7_cleaned_profile.png</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1331,7 +1331,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>appendix_materials/figures/appendix_I_testing_plots/day_ahead_forecast/total_cascade_day_ahead_forecast_with_benchmarks.png</t>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/day_ahead_forecast/total_cascade_day_ahead_forecast_with_benchmarks.png</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1355,7 +1355,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>233.42</v>
+        <v>225.04</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>appendix_materials/figures/appendix_I_testing_plots/error_analysis/rbfnn_actual_vs_predicted_scatter.png</t>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/error_analysis/rbfnn_actual_vs_predicted_scatter.png</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1410,7 +1410,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>358.82</v>
+        <v>360.88</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>appendix_materials/figures/appendix_I_testing_plots/error_analysis/rbfnn_residual_distribution.png</t>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/error_analysis/rbfnn_residual_distribution.png</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2368</t>
+          <t>2370</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1465,7 +1465,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>87.34999999999999</v>
+        <v>85.13</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>appendix_materials/figures/appendix_I_testing_plots/error_analysis/rbfnn_testing_mape_per_plant.png</t>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/error_analysis/rbfnn_testing_mape_per_plant.png</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1520,7 +1520,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>61.61</v>
+        <v>60.57</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>appendix_materials/figures/appendix_I_testing_plots/full_testing_split/agus1_testing_split_forecast_comparison.png</t>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/full_testing_split/agus1_testing_split_forecast_comparison.png</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>appendix_materials/figures/appendix_I_testing_plots/full_testing_split/agus2_testing_split_forecast_comparison.png</t>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/full_testing_split/agus2_testing_split_forecast_comparison.png</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>appendix_materials/figures/appendix_I_testing_plots/full_testing_split/agus4_testing_split_forecast_comparison.png</t>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/full_testing_split/agus4_testing_split_forecast_comparison.png</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1716,7 +1716,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>appendix_materials/figures/appendix_I_testing_plots/full_testing_split/agus5_testing_split_forecast_comparison.png</t>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/full_testing_split/agus5_testing_split_forecast_comparison.png</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>appendix_materials/figures/appendix_I_testing_plots/full_testing_split/agus6_testing_split_forecast_comparison.png</t>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/full_testing_split/agus6_testing_split_forecast_comparison.png</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>appendix_materials/figures/appendix_I_testing_plots/full_testing_split/agus7_testing_split_forecast_comparison.png</t>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/full_testing_split/agus7_testing_split_forecast_comparison.png</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1876,17 +1876,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>figure_4_13_agus1_testing_actual_vs_forecast.png</t>
+          <t>agus1_testing_actual_vs_rbfnn_forecast.png</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>appendix_materials/figures/appendix_I_testing_plots/testing_actual_vs_forecast/figure_4_13_agus1_testing_actual_vs_forecast.png</t>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/rbfnn_actual_vs_forecast/testing/agus1_testing_actual_vs_rbfnn_forecast.png</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>thesis_figures/testing_actual_vs_forecast/figure_4_13_agus1_testing_actual_vs_forecast.png</t>
+          <t>thesis_figures/rbfnn_actual_vs_forecast/testing/agus1_testing_actual_vs_rbfnn_forecast.png</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1896,20 +1896,20 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>3570</t>
+          <t>2321</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1466</t>
+          <t>846</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>330.82</v>
+        <v>186.02</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>RBFNN testing actual versus forecast plot for Agus 1</t>
+          <t>Appendix testing or forecasting plot for Agus 1</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
@@ -1931,17 +1931,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>figure_4_14_agus2_testing_actual_vs_forecast.png</t>
+          <t>agus2_testing_actual_vs_rbfnn_forecast.png</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>appendix_materials/figures/appendix_I_testing_plots/testing_actual_vs_forecast/figure_4_14_agus2_testing_actual_vs_forecast.png</t>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/rbfnn_actual_vs_forecast/testing/agus2_testing_actual_vs_rbfnn_forecast.png</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>thesis_figures/testing_actual_vs_forecast/figure_4_14_agus2_testing_actual_vs_forecast.png</t>
+          <t>thesis_figures/rbfnn_actual_vs_forecast/testing/agus2_testing_actual_vs_rbfnn_forecast.png</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1951,20 +1951,20 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>3570</t>
+          <t>2321</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>1466</t>
+          <t>846</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>246.79</v>
+        <v>151.97</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>RBFNN testing actual versus forecast plot for Agus 2</t>
+          <t>Appendix testing or forecasting plot for Agus 2</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -1986,17 +1986,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>figure_4_15_agus4_testing_actual_vs_forecast.png</t>
+          <t>agus4_testing_actual_vs_rbfnn_forecast.png</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>appendix_materials/figures/appendix_I_testing_plots/testing_actual_vs_forecast/figure_4_15_agus4_testing_actual_vs_forecast.png</t>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/rbfnn_actual_vs_forecast/testing/agus4_testing_actual_vs_rbfnn_forecast.png</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>thesis_figures/testing_actual_vs_forecast/figure_4_15_agus4_testing_actual_vs_forecast.png</t>
+          <t>thesis_figures/rbfnn_actual_vs_forecast/testing/agus4_testing_actual_vs_rbfnn_forecast.png</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2006,20 +2006,20 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>3570</t>
+          <t>2321</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1466</t>
+          <t>846</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>247.14</v>
+        <v>147.2</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>RBFNN testing actual versus forecast plot for Agus 4</t>
+          <t>Appendix testing or forecasting plot for Agus 4</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2041,17 +2041,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>figure_4_16_agus5_testing_actual_vs_forecast.png</t>
+          <t>agus5_testing_actual_vs_rbfnn_forecast.png</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>appendix_materials/figures/appendix_I_testing_plots/testing_actual_vs_forecast/figure_4_16_agus5_testing_actual_vs_forecast.png</t>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/rbfnn_actual_vs_forecast/testing/agus5_testing_actual_vs_rbfnn_forecast.png</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>thesis_figures/testing_actual_vs_forecast/figure_4_16_agus5_testing_actual_vs_forecast.png</t>
+          <t>thesis_figures/rbfnn_actual_vs_forecast/testing/agus5_testing_actual_vs_rbfnn_forecast.png</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2061,20 +2061,20 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>3570</t>
+          <t>2321</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1466</t>
+          <t>846</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>457.8</v>
+        <v>235.73</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>RBFNN testing actual versus forecast plot for Agus 5</t>
+          <t>Appendix testing or forecasting plot for Agus 5</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2096,17 +2096,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>figure_4_17_agus6_testing_actual_vs_forecast.png</t>
+          <t>agus6_testing_actual_vs_rbfnn_forecast.png</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>appendix_materials/figures/appendix_I_testing_plots/testing_actual_vs_forecast/figure_4_17_agus6_testing_actual_vs_forecast.png</t>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/rbfnn_actual_vs_forecast/testing/agus6_testing_actual_vs_rbfnn_forecast.png</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>thesis_figures/testing_actual_vs_forecast/figure_4_17_agus6_testing_actual_vs_forecast.png</t>
+          <t>thesis_figures/rbfnn_actual_vs_forecast/testing/agus6_testing_actual_vs_rbfnn_forecast.png</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2116,20 +2116,20 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>3570</t>
+          <t>2321</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>1466</t>
+          <t>846</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>233.6</v>
+        <v>141.83</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>RBFNN testing actual versus forecast plot for Agus 6</t>
+          <t>Appendix testing or forecasting plot for Agus 6</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2151,17 +2151,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>figure_4_18_agus7_testing_actual_vs_forecast.png</t>
+          <t>agus7_testing_actual_vs_rbfnn_forecast.png</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>appendix_materials/figures/appendix_I_testing_plots/testing_actual_vs_forecast/figure_4_18_agus7_testing_actual_vs_forecast.png</t>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/rbfnn_actual_vs_forecast/testing/agus7_testing_actual_vs_rbfnn_forecast.png</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>thesis_figures/testing_actual_vs_forecast/figure_4_18_agus7_testing_actual_vs_forecast.png</t>
+          <t>thesis_figures/rbfnn_actual_vs_forecast/testing/agus7_testing_actual_vs_rbfnn_forecast.png</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2171,20 +2171,20 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>3570</t>
+          <t>2321</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1466</t>
+          <t>846</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>435.88</v>
+        <v>224.87</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>RBFNN testing actual versus forecast plot for Agus 7</t>
+          <t>Appendix testing or forecasting plot for Agus 7</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2206,17 +2206,17 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>rbfnn_testing_mape_per_plant_maroon.png</t>
+          <t>all_plants_testing_actual_vs_rbfnn_forecast.png</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>appendix_materials/figures/appendix_I_testing_plots/testing_metrics/rbfnn_testing_mape_per_plant_maroon.png</t>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/rbfnn_actual_vs_forecast/testing/all_plants_testing_actual_vs_rbfnn_forecast.png</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>thesis_figures/testing_metrics/rbfnn_testing_mape_per_plant_maroon.png</t>
+          <t>thesis_figures/rbfnn_actual_vs_forecast/testing/all_plants_testing_actual_vs_rbfnn_forecast.png</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2226,20 +2226,20 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>3150</t>
+          <t>2682</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>99.36</v>
+        <v>513.67</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>RBFNN testing metric plot</t>
+          <t>Appendix testing or forecasting plot for all Agus plants</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -2261,17 +2261,17 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>rbfnn_validation_mape_per_plant.png</t>
+          <t>agus1_validation_actual_vs_rbfnn_forecast.png</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>appendix_materials/figures/appendix_I_testing_plots/validation_metrics/rbfnn_validation_mape_per_plant.png</t>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/rbfnn_actual_vs_forecast/validation/agus1_validation_actual_vs_rbfnn_forecast.png</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>thesis_figures/validation_metrics/rbfnn_validation_mape_per_plant.png</t>
+          <t>thesis_figures/rbfnn_actual_vs_forecast/validation/agus1_validation_actual_vs_rbfnn_forecast.png</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2281,20 +2281,20 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>3150</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1860</t>
+          <t>846</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>103.84</v>
+        <v>197.81</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>RBFNN validation metric plot</t>
+          <t>Appendix testing or forecasting plot for Agus 1</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
@@ -2311,22 +2311,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Appendix E</t>
+          <t>Appendix I</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>appendix_E_planned_outage_template.png</t>
+          <t>agus2_validation_actual_vs_rbfnn_forecast.png</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>appendix_materials/screenshots/appendix_E_planned_outage_template.png</t>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/rbfnn_actual_vs_forecast/validation/agus2_validation_actual_vs_rbfnn_forecast.png</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>outputs/outages_planning/Planned_Outages_Input.xlsx</t>
+          <t>thesis_figures/rbfnn_actual_vs_forecast/validation/agus2_validation_actual_vs_rbfnn_forecast.png</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2336,20 +2336,20 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>4599</t>
+          <t>2317</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>1872</t>
+          <t>846</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>130.99</v>
+        <v>151.21</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Screenshot-style table image of the 24-hour planned outage input template.</t>
+          <t>Appendix testing or forecasting plot for Agus 2</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -2366,55 +2366,1760 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
+          <t>Appendix I</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>agus4_validation_actual_vs_rbfnn_forecast.png</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/rbfnn_actual_vs_forecast/validation/agus4_validation_actual_vs_rbfnn_forecast.png</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>thesis_figures/rbfnn_actual_vs_forecast/validation/agus4_validation_actual_vs_rbfnn_forecast.png</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>PNG image</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>846</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>132.33</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Appendix testing or forecasting plot for Agus 4</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Use as an appendix figure or supporting visual reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>P036</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Appendix I</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>agus5_validation_actual_vs_rbfnn_forecast.png</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/rbfnn_actual_vs_forecast/validation/agus5_validation_actual_vs_rbfnn_forecast.png</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>thesis_figures/rbfnn_actual_vs_forecast/validation/agus5_validation_actual_vs_rbfnn_forecast.png</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>PNG image</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>846</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>229.37</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Appendix testing or forecasting plot for Agus 5</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Use as an appendix figure or supporting visual reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>P037</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Appendix I</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>agus6_validation_actual_vs_rbfnn_forecast.png</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/rbfnn_actual_vs_forecast/validation/agus6_validation_actual_vs_rbfnn_forecast.png</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>thesis_figures/rbfnn_actual_vs_forecast/validation/agus6_validation_actual_vs_rbfnn_forecast.png</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>PNG image</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>846</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>245.32</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Appendix testing or forecasting plot for Agus 6</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Use as an appendix figure or supporting visual reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>P038</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Appendix I</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>agus7_validation_actual_vs_rbfnn_forecast.png</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/rbfnn_actual_vs_forecast/validation/agus7_validation_actual_vs_rbfnn_forecast.png</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>thesis_figures/rbfnn_actual_vs_forecast/validation/agus7_validation_actual_vs_rbfnn_forecast.png</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>PNG image</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>846</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>220.64</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Appendix testing or forecasting plot for Agus 7</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Use as an appendix figure or supporting visual reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>P039</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Appendix I</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>all_plants_validation_actual_vs_rbfnn_forecast.png</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/rbfnn_actual_vs_forecast/validation/all_plants_validation_actual_vs_rbfnn_forecast.png</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>thesis_figures/rbfnn_actual_vs_forecast/validation/all_plants_validation_actual_vs_rbfnn_forecast.png</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>PNG image</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>2679</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>559.75</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Appendix testing or forecasting plot for all Agus plants</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Use as an appendix figure or supporting visual reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>P040</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Appendix I</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>agus1_testing_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/rbfnn_outage_informed_actual_vs_forecast/testing/agus1_testing_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>thesis_figures/rbfnn_outage_informed_actual_vs_forecast/testing/agus1_testing_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>PNG image</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>2340</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>864</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>191.11</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Appendix testing or forecasting plot for Agus 1</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Use as an appendix figure or supporting visual reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>P041</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Appendix I</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>agus2_testing_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/rbfnn_outage_informed_actual_vs_forecast/testing/agus2_testing_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>thesis_figures/rbfnn_outage_informed_actual_vs_forecast/testing/agus2_testing_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>PNG image</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2340</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>864</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>145.29</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Appendix testing or forecasting plot for Agus 2</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Use as an appendix figure or supporting visual reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>P042</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Appendix I</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>agus4_testing_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/rbfnn_outage_informed_actual_vs_forecast/testing/agus4_testing_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>thesis_figures/rbfnn_outage_informed_actual_vs_forecast/testing/agus4_testing_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>PNG image</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>2340</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>864</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>143.12</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Appendix testing or forecasting plot for Agus 4</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Use as an appendix figure or supporting visual reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>P043</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Appendix I</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>agus5_testing_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/rbfnn_outage_informed_actual_vs_forecast/testing/agus5_testing_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>thesis_figures/rbfnn_outage_informed_actual_vs_forecast/testing/agus5_testing_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>PNG image</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>2340</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>864</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>238.68</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Appendix testing or forecasting plot for Agus 5</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Use as an appendix figure or supporting visual reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>P044</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Appendix I</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>agus6_testing_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/rbfnn_outage_informed_actual_vs_forecast/testing/agus6_testing_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>thesis_figures/rbfnn_outage_informed_actual_vs_forecast/testing/agus6_testing_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>PNG image</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2340</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>864</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>135.52</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Appendix testing or forecasting plot for Agus 6</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Use as an appendix figure or supporting visual reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>P045</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Appendix I</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>agus7_testing_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/rbfnn_outage_informed_actual_vs_forecast/testing/agus7_testing_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>thesis_figures/rbfnn_outage_informed_actual_vs_forecast/testing/agus7_testing_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>PNG image</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2340</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>864</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>230.17</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Appendix testing or forecasting plot for Agus 7</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Use as an appendix figure or supporting visual reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>P046</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Appendix I</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>all_plants_testing_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/rbfnn_outage_informed_actual_vs_forecast/testing/all_plants_testing_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>thesis_figures/rbfnn_outage_informed_actual_vs_forecast/testing/all_plants_testing_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>PNG image</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2700</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>498.96</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Appendix testing or forecasting plot for all Agus plants</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Use as an appendix figure or supporting visual reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>P047</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Appendix I</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>agus1_validation_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/rbfnn_outage_informed_actual_vs_forecast/validation/agus1_validation_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>thesis_figures/rbfnn_outage_informed_actual_vs_forecast/validation/agus1_validation_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>PNG image</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2340</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>864</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>203.64</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Appendix testing or forecasting plot for Agus 1</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Use as an appendix figure or supporting visual reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>P048</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Appendix I</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>agus2_validation_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/rbfnn_outage_informed_actual_vs_forecast/validation/agus2_validation_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>thesis_figures/rbfnn_outage_informed_actual_vs_forecast/validation/agus2_validation_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>PNG image</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2340</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>864</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>147.42</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Appendix testing or forecasting plot for Agus 2</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Use as an appendix figure or supporting visual reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>P049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Appendix I</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>agus4_validation_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/rbfnn_outage_informed_actual_vs_forecast/validation/agus4_validation_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>thesis_figures/rbfnn_outage_informed_actual_vs_forecast/validation/agus4_validation_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>PNG image</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>2340</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>864</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>127.98</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Appendix testing or forecasting plot for Agus 4</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Use as an appendix figure or supporting visual reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>P050</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Appendix I</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>agus5_validation_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/rbfnn_outage_informed_actual_vs_forecast/validation/agus5_validation_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>thesis_figures/rbfnn_outage_informed_actual_vs_forecast/validation/agus5_validation_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>PNG image</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2340</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>864</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>239.8</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Appendix testing or forecasting plot for Agus 5</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Use as an appendix figure or supporting visual reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>P051</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Appendix I</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>agus6_validation_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/rbfnn_outage_informed_actual_vs_forecast/validation/agus6_validation_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>thesis_figures/rbfnn_outage_informed_actual_vs_forecast/validation/agus6_validation_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>PNG image</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>2340</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>864</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>252.47</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>Appendix testing or forecasting plot for Agus 6</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Use as an appendix figure or supporting visual reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>P052</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Appendix I</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>agus7_validation_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/rbfnn_outage_informed_actual_vs_forecast/validation/agus7_validation_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>thesis_figures/rbfnn_outage_informed_actual_vs_forecast/validation/agus7_validation_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>PNG image</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>2340</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>864</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>228.39</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Appendix testing or forecasting plot for Agus 7</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Use as an appendix figure or supporting visual reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>P053</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Appendix I</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>all_plants_validation_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/rbfnn_outage_informed_actual_vs_forecast/validation/all_plants_validation_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>thesis_figures/rbfnn_outage_informed_actual_vs_forecast/validation/all_plants_validation_actual_vs_rbfnn_outage_informed_forecast.png</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>PNG image</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>2700</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>1800</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>562.73</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Appendix testing or forecasting plot for all Agus plants</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Use as an appendix figure or supporting visual reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>P054</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Appendix I</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>figure_4_13_agus1_testing_actual_vs_forecast.png</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/testing_actual_vs_forecast/figure_4_13_agus1_testing_actual_vs_forecast.png</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>thesis_figures/testing_actual_vs_forecast/figure_4_13_agus1_testing_actual_vs_forecast.png</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>PNG image</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>3570</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>1466</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>336.96</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>RBFNN testing actual versus forecast plot for Agus 1</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Use as an appendix figure or supporting visual reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>P055</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Appendix I</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>figure_4_14_agus2_testing_actual_vs_forecast.png</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/testing_actual_vs_forecast/figure_4_14_agus2_testing_actual_vs_forecast.png</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>thesis_figures/testing_actual_vs_forecast/figure_4_14_agus2_testing_actual_vs_forecast.png</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>PNG image</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>3570</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>1466</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>257.06</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>RBFNN testing actual versus forecast plot for Agus 2</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Use as an appendix figure or supporting visual reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>P056</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Appendix I</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>figure_4_15_agus4_testing_actual_vs_forecast.png</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/testing_actual_vs_forecast/figure_4_15_agus4_testing_actual_vs_forecast.png</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>thesis_figures/testing_actual_vs_forecast/figure_4_15_agus4_testing_actual_vs_forecast.png</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>PNG image</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>3570</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>1466</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>251.77</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>RBFNN testing actual versus forecast plot for Agus 4</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Use as an appendix figure or supporting visual reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>P057</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Appendix I</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>figure_4_16_agus5_testing_actual_vs_forecast.png</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/testing_actual_vs_forecast/figure_4_16_agus5_testing_actual_vs_forecast.png</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>thesis_figures/testing_actual_vs_forecast/figure_4_16_agus5_testing_actual_vs_forecast.png</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>PNG image</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>3570</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>1466</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>448.77</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>RBFNN testing actual versus forecast plot for Agus 5</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Use as an appendix figure or supporting visual reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>P058</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Appendix I</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>figure_4_17_agus6_testing_actual_vs_forecast.png</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/testing_actual_vs_forecast/figure_4_17_agus6_testing_actual_vs_forecast.png</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>thesis_figures/testing_actual_vs_forecast/figure_4_17_agus6_testing_actual_vs_forecast.png</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>PNG image</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>3570</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>1466</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>237.25</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>RBFNN testing actual versus forecast plot for Agus 6</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Use as an appendix figure or supporting visual reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>P059</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Appendix I</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>figure_4_18_agus7_testing_actual_vs_forecast.png</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/testing_actual_vs_forecast/figure_4_18_agus7_testing_actual_vs_forecast.png</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>thesis_figures/testing_actual_vs_forecast/figure_4_18_agus7_testing_actual_vs_forecast.png</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>PNG image</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>3570</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>1466</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>431.4</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>RBFNN testing actual versus forecast plot for Agus 7</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Use as an appendix figure or supporting visual reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>P060</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Appendix I</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>rbfnn_testing_mape_per_plant_maroon.png</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/testing_metrics/rbfnn_testing_mape_per_plant_maroon.png</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>thesis_figures/testing_metrics/rbfnn_testing_mape_per_plant_maroon.png</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>PNG image</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>3150</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>1860</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>99.36</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>RBFNN testing metric plot</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Use as an appendix figure or supporting visual reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>P061</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Appendix I</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>rbfnn_validation_mape_per_plant.png</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>PAPER CONTEXT/figures/appendix_I_testing_plots/validation_metrics/rbfnn_validation_mape_per_plant.png</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>thesis_figures/validation_metrics/rbfnn_validation_mape_per_plant.png</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>PNG image</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>3150</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>1860</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>103.84</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>RBFNN validation metric plot</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Use as an appendix figure or supporting visual reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>P062</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Appendix figure</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>thesis_code_block_diagram_clear.png</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>PAPER CONTEXT/figures/thesis_code_block_diagram_clear.png</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Generated inside appendix_materials</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>PNG image</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>2600</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>1750</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>298.47</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Appendix image file: thesis code block diagram clear.</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Use as an appendix figure or supporting visual reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>P063</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Appendix figure</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>thesis_code_block_diagram_neat.png</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>PAPER CONTEXT/figures/thesis_code_block_diagram_neat.png</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Generated inside appendix_materials</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>PNG image</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>2200</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>3300</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>322.36</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Appendix image file: thesis code block diagram neat.</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Use as an appendix figure or supporting visual reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>P064</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Appendix figure</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>thesis_code_block_diagram_portrait_top_to_bottom.png</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>PAPER CONTEXT/figures/thesis_code_block_diagram_portrait_top_to_bottom.png</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Generated inside appendix_materials</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>PNG image</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>3600</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>329.41</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Appendix image file: thesis code block diagram portrait top to bottom.</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Use as an appendix figure or supporting visual reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>P065</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Appendix E</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>appendix_E_planned_outage_template.png</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>PAPER CONTEXT/screenshots/appendix_E_planned_outage_template.png</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>outputs/outages_planning/Planned_Outages_Input.xlsx</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>PNG image</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>4599</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>1872</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>130.99</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Screenshot-style table image of the 24-hour planned outage input template.</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Use as an appendix figure or supporting visual reference.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>P066</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
           <t>Appendix F</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C67" t="inlineStr">
         <is>
           <t>appendix_F_day_ahead_forecast_output.png</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>appendix_materials/screenshots/appendix_F_day_ahead_forecast_output.png</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>PAPER CONTEXT/screenshots/appendix_F_day_ahead_forecast_output.png</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
         <is>
           <t>outputs/rbfnn_forecast/Day_Ahead_24H_RBFNN_Forecast.xlsx</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>PNG image</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>PNG image</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
         <is>
           <t>4662</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>1872</t>
         </is>
       </c>
-      <c r="I36" t="n">
-        <v>624.55</v>
-      </c>
-      <c r="J36" t="inlineStr">
+      <c r="I67" t="n">
+        <v>622.77</v>
+      </c>
+      <c r="J67" t="inlineStr">
         <is>
           <t>Screenshot-style table image of the 24-hour day-ahead RBFNN forecast output.</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>Use as an appendix figure or supporting visual reference.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K36"/>
+  <autoFilter ref="A1:K67"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>